--- a/backtest_runs/20260410_193731/by_symbol/HWQS/HWQS.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/HWQS/HWQS.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-2732</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>102240.24</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>102240.24</v>
@@ -863,7 +863,7 @@
         <v>-3660.87999999999</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>105791.84</v>
@@ -1139,7 +1139,7 @@
         <v>-6611.440000000005</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>116173.44</v>
@@ -1231,7 +1231,7 @@
         <v>-6065.039999999997</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>114479.6</v>
@@ -1277,7 +1277,7 @@
         <v>-9070.240000000002</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>105409.36</v>
@@ -1369,7 +1369,7 @@
         <v>-3442.320000000014</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>108469.2</v>
@@ -1461,7 +1461,7 @@
         <v>-4917.599999999992</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>103551.6</v>
